--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,133 +26,142 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpCatsEye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActLulwyTrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrainBlood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrainMana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">breathe_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ball_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flare_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comet_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bolt_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arrow_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missile_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miasma_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpTelekinesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMoonArrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMoonSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMeteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpEarthquake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpShutterHex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpSilence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealLight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealHeavy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealCritical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealTouch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealEris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealOdina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealJure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActManaAbsorb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActJureHeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funnel_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActSummonGodPet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActSummonUndeadSister</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpTeleport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpReturn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpEvac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 16.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 18.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.222</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.338 Patch 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpCatsEye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActLulwyTrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrainBlood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrainMana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">breathe_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ball_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flare_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comet_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bolt_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hand_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arrow_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miasma_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sword_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpTelekinesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMoonArrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMoonSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMeteor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpEarthquake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpShutterHex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpSilence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealLight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealHeavy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealCritical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealEris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealOdina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealJure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActManaAbsorb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActJureHeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">funnel_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActSummonGodPet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActSummonUndeadSister</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpTeleport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpReturn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpEvac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 16.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 18.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.222</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.120</t>
@@ -252,7 +261,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -260,7 +269,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -268,7 +277,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -276,7 +285,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -284,7 +293,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -292,7 +301,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -300,7 +309,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -308,7 +317,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -316,7 +325,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -324,7 +333,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -332,7 +341,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -340,7 +349,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
@@ -348,7 +357,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -356,7 +365,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -364,7 +373,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -372,7 +381,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -380,7 +389,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -388,7 +397,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -396,7 +405,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
@@ -404,7 +413,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -412,7 +421,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
@@ -420,7 +429,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -428,7 +437,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -436,7 +445,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
@@ -444,7 +453,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
@@ -452,7 +461,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
@@ -460,7 +469,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
@@ -468,7 +477,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -476,7 +485,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
@@ -484,7 +493,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
@@ -492,7 +501,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
@@ -500,7 +509,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
@@ -508,7 +517,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -516,7 +525,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -524,7 +533,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
@@ -532,7 +541,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
@@ -540,7 +549,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -548,7 +557,23 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="58">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,142 +26,145 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpCatsEye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActLulwyTrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrainBlood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrainMana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">breathe_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ball_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flare_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comet_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bolt_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arrow_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missile_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miasma_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpTelekinesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMoonArrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMoonSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMeteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpEarthquake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpShutterHex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpSilence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealLight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealHeavy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealCritical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealTouch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealEris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealOdina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealJure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActManaAbsorb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActJureHeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funnel_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActSummonGodPet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActSummonUndeadSister</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpTeleport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpReturn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpEvac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 16.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 18.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpCatsEye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActLulwyTrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrainBlood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrainMana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">breathe_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ball_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flare_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comet_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bolt_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hand_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arrow_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">missile_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miasma_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sword_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpTelekinesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMoonArrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMoonSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMeteor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpEarthquake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpShutterHex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpSilence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealLight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealHeavy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealCritical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealTouch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealEris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealOdina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealJure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActManaAbsorb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActJureHeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">funnel_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActSummonGodPet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActSummonUndeadSister</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpTeleport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpReturn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpEvac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 16.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 18.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.120</t>
@@ -365,7 +368,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -381,7 +384,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -389,7 +392,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -397,7 +400,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
@@ -405,7 +408,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -421,7 +424,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
@@ -429,7 +432,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -453,7 +456,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
@@ -461,7 +464,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -469,7 +472,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -477,7 +480,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
@@ -485,7 +488,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
@@ -493,7 +496,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
@@ -501,7 +504,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -573,7 +576,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
